--- a/reports/二级子公司D_现金流量表_2026-02.xlsx
+++ b/reports/二级子公司D_现金流量表_2026-02.xlsx
@@ -1957,16 +1957,8 @@
           <t>1</t>
         </is>
       </c>
-      <c r="F3" s="28" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
-      <c r="G3" s="28" t="inlineStr">
-        <is>
-          <t>－</t>
-        </is>
-      </c>
+      <c r="F3" s="28" t="n"/>
+      <c r="G3" s="28" t="n"/>
       <c r="I3" s="5" t="n"/>
     </row>
     <row r="4" ht="18" customHeight="1">
@@ -1996,10 +1988,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>63629280</v>
+        <v>61836882</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>127258560</v>
+        <v>123898661</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2030,10 +2022,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>1263772</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>2521975</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2063,10 +2055,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>630111</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>1263201</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2096,10 +2088,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>316850</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>632269</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2129,10 +2121,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>251469</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>503916</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2162,10 +2154,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>190384</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>380236</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2195,10 +2187,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>125676</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>251535</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2228,10 +2220,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>95138</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>190282</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2261,10 +2253,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>62935</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>125772</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2294,10 +2286,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>158192</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>316842</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2327,10 +2319,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>79304</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>158296</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2360,10 +2352,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>50137</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>100503</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2393,10 +2385,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>163152</v>
+        <v>158819</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>326304</v>
+        <v>316892</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2426,10 +2418,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>1087680</v>
+        <v>1051923</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>2175360</v>
+        <v>2108456</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2546,7 +2538,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>64880112</v>
+        <v>66271592</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2577,10 +2569,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>41694400</v>
+        <v>40600155</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>83388800</v>
+        <v>81282322</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2610,10 +2602,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>420348</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>839315</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2643,10 +2635,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>315722</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>632768</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2676,10 +2668,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>210846</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>420710</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2709,10 +2701,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>157386</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>315506</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2742,10 +2734,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>105687</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>210938</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2775,10 +2767,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>78957</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>158169</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2808,10 +2800,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>6526080</v>
+        <v>6367609</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>13052160</v>
+        <v>12722899</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2841,10 +2833,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>3444320</v>
+        <v>3328547</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>6888640</v>
+        <v>6658666</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2874,10 +2866,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>1359600</v>
+        <v>1324977</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>2719200</v>
+        <v>2651344</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2936,7 +2928,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>53024400</v>
+        <v>52910234</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2967,7 +2959,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>11855712</v>
+        <v>13361358</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -3093,10 +3085,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>82400</v>
+        <v>80395</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>164800</v>
+        <v>160564</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3159,10 +3151,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>721000</v>
+        <v>703075</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>1442000</v>
+        <v>1406171</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3192,10 +3184,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>432600</v>
+        <v>418572</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>865200</v>
+        <v>836499</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3225,7 +3217,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>803400</v>
+        <v>783470</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3256,10 +3248,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>8240000</v>
+        <v>7996069</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>16480000</v>
+        <v>15960760</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3289,10 +3281,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>1236000</v>
+        <v>1198654</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>2472000</v>
+        <v>2402774</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3322,10 +3314,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>5665000</v>
+        <v>5514400</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>11330000</v>
+        <v>11002884</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3454,10 +3446,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>185400</v>
+        <v>180865</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>370800</v>
+        <v>361551</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3487,7 +3479,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>8425400</v>
+        <v>8176934</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3518,7 +3510,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-7622000</v>
+        <v>-7393464</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3578,10 +3570,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>1545000</v>
+        <v>1499942</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>3090000</v>
+        <v>3006152</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3644,10 +3636,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>2575000</v>
+        <v>2492363</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>5150000</v>
+        <v>4996365</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3677,10 +3669,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>2575000</v>
+        <v>2510396</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>5150000</v>
+        <v>5010382</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3710,10 +3702,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>82400</v>
+        <v>79614</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>164800</v>
+        <v>159487</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3743,7 +3735,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>4202400</v>
+        <v>4071919</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3774,10 +3766,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>2060000</v>
+        <v>1990734</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>4120000</v>
+        <v>3982467</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3807,10 +3799,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>2060000</v>
+        <v>2007581</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>4120000</v>
+        <v>4017211</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3840,10 +3832,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>329600</v>
+        <v>319183</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>659200</v>
+        <v>637585</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3902,10 +3894,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>288400</v>
+        <v>280159</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>576800</v>
+        <v>559090</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3935,10 +3927,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>41200</v>
+        <v>39915</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>82400</v>
+        <v>80019</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3968,7 +3960,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>2430800</v>
+        <v>2349832</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3999,7 +3991,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>1771600</v>
+        <v>1722087</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -4059,7 +4051,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>6005312</v>
+        <v>7689981</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -4090,7 +4082,9 @@
         </is>
       </c>
       <c r="F69" s="23" t="n"/>
-      <c r="G69" s="20" t="n"/>
+      <c r="G69" s="20" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="70" ht="18" customHeight="1">
       <c r="A70" s="9" t="inlineStr">
@@ -4119,7 +4113,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>6005312</v>
+        <v>7689981</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
